--- a/results/VALIDATION_REPORT.xlsx
+++ b/results/VALIDATION_REPORT.xlsx
@@ -19,6 +19,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QSAR model card" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monte Carlo E1 dose range" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monte Carlo E2 power" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Solvent confound" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2054,6 +2055,288 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>conc_ppm</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>viab_trial1</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>viab_trial2</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>viab_mean</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>viab_sd</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>dmso_pct_if_direct</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>over_routine_limit</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>over_toxic_threshold</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>inhibition_pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MBEE</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="C2" t="n">
+        <v>105.01</v>
+      </c>
+      <c r="D2" t="n">
+        <v>135.59</v>
+      </c>
+      <c r="E2" t="n">
+        <v>120.3</v>
+      </c>
+      <c r="F2" t="n">
+        <v>21.62</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="H2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-20.3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MBEE</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>25</v>
+      </c>
+      <c r="C3" t="n">
+        <v>98.76000000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>115.88</v>
+      </c>
+      <c r="E3" t="n">
+        <v>107.32</v>
+      </c>
+      <c r="F3" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-7.319999999999993</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>MBEE</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>50</v>
+      </c>
+      <c r="C4" t="n">
+        <v>97.53</v>
+      </c>
+      <c r="D4" t="n">
+        <v>108.92</v>
+      </c>
+      <c r="E4" t="n">
+        <v>103.22</v>
+      </c>
+      <c r="F4" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-3.219999999999999</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MBEE</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>80.64</v>
+      </c>
+      <c r="D5" t="n">
+        <v>101.67</v>
+      </c>
+      <c r="E5" t="n">
+        <v>91.16</v>
+      </c>
+      <c r="F5" t="n">
+        <v>14.87</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>8.840000000000003</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MBEE</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>200</v>
+      </c>
+      <c r="C6" t="n">
+        <v>70.88</v>
+      </c>
+      <c r="D6" t="n">
+        <v>96.23</v>
+      </c>
+      <c r="E6" t="n">
+        <v>83.56</v>
+      </c>
+      <c r="F6" t="n">
+        <v>17.92</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>16.44</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MBEE</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>400</v>
+      </c>
+      <c r="C7" t="n">
+        <v>55.37</v>
+      </c>
+      <c r="D7" t="n">
+        <v>74.70999999999999</v>
+      </c>
+      <c r="E7" t="n">
+        <v>65.04000000000001</v>
+      </c>
+      <c r="F7" t="n">
+        <v>13.67</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>34.95999999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
